--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfc8bfccf62704c6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra9de661d54ac4c6e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra9de661d54ac4c6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R69e2e49762844c7c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R69e2e49762844c7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb8a1008a815944d9"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb8a1008a815944d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra38b6262abe64170"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra38b6262abe64170"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3c1288446b474ee9"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3c1288446b474ee9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re7acf65d722a4cfa"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re7acf65d722a4cfa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9b21588bbd024f07"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9b21588bbd024f07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R233cd736baf74054"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R233cd736baf74054"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4ff3c654eeb84d4a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4ff3c654eeb84d4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4f0ca1b9654b4bd1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4f0ca1b9654b4bd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4454af550c00410a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4454af550c00410a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R205ecd04b7fb4cff"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R205ecd04b7fb4cff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra401afc23ea14387"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra401afc23ea14387"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdaa1904069c34314"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdaa1904069c34314"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9453a5b76e9e4060"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9453a5b76e9e4060"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6f678c53ecac4cd1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_TextLength/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6f678c53ecac4cd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf711672638ec4c29"/>
   </x:sheets>
 </x:workbook>
 </file>
